--- a/top_products.xlsx
+++ b/top_products.xlsx
@@ -455,13 +455,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4400592.800400055</v>
+        <v>4400592.8004</v>
       </c>
       <c r="D2" t="n">
         <v>2977</v>
       </c>
       <c r="E2" t="n">
-        <v>1730.148538977626</v>
+        <v>1730.148538977636</v>
       </c>
     </row>
     <row r="3">
@@ -476,13 +476,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4009494.761841063</v>
+        <v>4009494.761841</v>
       </c>
       <c r="D3" t="n">
         <v>2664</v>
       </c>
       <c r="E3" t="n">
-        <v>1776.319882412901</v>
+        <v>1776.319882412914</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3693678.025272058</v>
+        <v>3693678.025272</v>
       </c>
       <c r="D4" t="n">
         <v>2394</v>
       </c>
       <c r="E4" t="n">
-        <v>1819.61832230346</v>
+        <v>1819.618322303473</v>
       </c>
     </row>
     <row r="5">
@@ -518,13 +518,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3438478.860423046</v>
+        <v>3438478.860423</v>
       </c>
       <c r="D5" t="n">
         <v>2234</v>
       </c>
       <c r="E5" t="n">
-        <v>1812.015757788449</v>
+        <v>1812.015757788462</v>
       </c>
     </row>
     <row r="6">
@@ -539,13 +539,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3434256.94192805</v>
+        <v>3434256.941928</v>
       </c>
       <c r="D6" t="n">
         <v>2216</v>
       </c>
       <c r="E6" t="n">
-        <v>1821.137118216307</v>
+        <v>1821.137118216319</v>
       </c>
     </row>
     <row r="7">
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3309673.216908046</v>
+        <v>3309673.216908</v>
       </c>
       <c r="D7" t="n">
         <v>2111</v>
       </c>
       <c r="E7" t="n">
-        <v>1836.217991973547</v>
+        <v>1836.21799197356</v>
       </c>
     </row>
     <row r="8">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2516857.314918006</v>
+        <v>2516857.314918</v>
       </c>
       <c r="D8" t="n">
         <v>1642</v>
       </c>
       <c r="E8" t="n">
-        <v>1745.138601418444</v>
+        <v>1745.13860141844</v>
       </c>
     </row>
     <row r="9">
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2347655.953454014</v>
+        <v>2347655.953454</v>
       </c>
       <c r="D9" t="n">
         <v>1498</v>
       </c>
       <c r="E9" t="n">
-        <v>1776.76499901686</v>
+        <v>1776.764999016854</v>
       </c>
     </row>
     <row r="10">
@@ -623,13 +623,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2012447.775000018</v>
+        <v>2012447.775</v>
       </c>
       <c r="D10" t="n">
         <v>1245</v>
       </c>
       <c r="E10" t="n">
-        <v>1823.773167166421</v>
+        <v>1823.773167166417</v>
       </c>
     </row>
     <row r="11">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1847818.628000009</v>
+        <v>1847818.628</v>
       </c>
       <c r="D11" t="n">
         <v>664</v>
       </c>
       <c r="E11" t="n">
-        <v>3035.879600000022</v>
+        <v>3035.8796</v>
       </c>
     </row>
   </sheetData>
